--- a/Assets/GameSample/Forms/Excels/Story/ModText_TextBase.xlsx
+++ b/Assets/GameSample/Forms/Excels/Story/ModText_TextBase.xlsx
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D360"/>
+  <dimension ref="A1:D361"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="16" customWidth="1" style="1" min="1" max="1"/>
@@ -8113,6 +8113,26 @@
       <c r="D360" s="0" t="inlineStr">
         <is>
           <t>前景 WangTile</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="0" t="n">
+        <v>1000367</v>
+      </c>
+      <c r="B361" s="0" t="inlineStr">
+        <is>
+          <t>noAvailableOperations</t>
+        </is>
+      </c>
+      <c r="C361" s="0" t="inlineStr">
+        <is>
+          <t>No available operations</t>
+        </is>
+      </c>
+      <c r="D361" s="0" t="inlineStr">
+        <is>
+          <t>没有可用的操作</t>
         </is>
       </c>
     </row>

--- a/Assets/GameSample/Forms/Excels/Story/ModText_TextBase.xlsx
+++ b/Assets/GameSample/Forms/Excels/Story/ModText_TextBase.xlsx
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D361"/>
+  <dimension ref="A1:D363"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="16" customWidth="1" style="1" min="1" max="1"/>
@@ -8047,12 +8047,12 @@
       </c>
       <c r="C357" s="0" t="inlineStr">
         <is>
-          <t>Story commands (command names are case-insensitive)\n\nFor every supported data type:\nAddStory&lt;Type&gt; "name" - create data from that type's default row.\nDelStory&lt;Type&gt; "name" - delete the named data.\nCopyStory&lt;Type&gt; "name" - copy it; duplicate names receive Copy, Copy 2, and so on.\nSetStory&lt;Type&gt; "name" {JSON} - update only the supplied JSON fields.\n\nAll Story commands:\nCharacter: AddStoryCharacter, DelStoryCharacter, CopyStoryCharacter, SetStoryCharacter\nItem: AddStoryItem, DelStoryItem, CopyStoryItem, SetStoryItem\nSkill: AddStorySkill, DelStorySkill, CopyStorySkill, SetStorySkill\nSceneObject: AddStorySceneObject, DelStorySceneObject, CopyStorySceneObject, SetStorySceneObject\nEffect: AddStoryEffect, DelStoryEffect, CopyStoryEffect, SetStoryEffect\nEvent: AddStoryEvent, DelStoryEvent, CopyStoryEvent, SetStoryEvent\nMission: AddStoryMission, DelStoryMission, CopyStoryMission, SetStoryMission\nTile: AddStoryTile, DelStoryTile, CopyStoryTile, SetStoryTile\n\nSetStory JSON fields:\nCharacter: name(string), labId(int), avatarTex(int), paramDic(dictionary), protoUid(int), animDic(dictionary), defaultAnimName(dictionary), faceType(enum int), speedParamName(string), hpParamName(string), events(dictionary), equips(dictionary), desc(string), illustration(int), unique(bool), skill(dictionary), recoveryTime(float), enableNav(bool), minimapIcon(int), size(int), passType(list&lt;int&gt;).\nItem: name(string), labId(int), iconTexName(int), paramDic(dictionary), protoUid(int), model(object), desc(string), amount(int), maxAmountPer(int), equip(enum int), styleTex(dictionary), price(int), canEquipe(bool), events(dictionary), isConsume(bool), paramDicCharacter(dictionary), minimapIcon(int).\nSkill: name(string), labId(int), protoUid(int), icon(int), paramDic(dictionary), skillTypes(list&lt;enum int&gt;), characterUid(int), cd(float), lastUseTime(float), events(dictionary), triggerConditionUid(int).\nSceneObject: name(string), icon(int), model(object), labId(int), collision(bool), events(dictionary), paramDic(dictionary), minimapIcon(int), faceType(enum int), animClip(dictionary).\nEffect: name(string), labId(int), clips(list&lt;list&lt;EffectClip&gt;&gt;), ground(bool).\nEvent: name(string), code(string), zCode(list&lt;string&gt;), zCodeMap(list&lt;int&gt;), paramCount(int), returnValue(string), labId(int).\nMission: name(string), labId(int), desc(string), show(bool), received(bool), done(bool), fail(bool), targetSceneId(int), targetPos(Vector3), radius(float).\nTile: name(string), icon(int), animTimeInterval(float), texs(list&lt;int&gt;), labId(int), events(dictionary), isWangTile(bool), passType(int), enableFrontPart(bool), frontPartTexs(list&lt;int&gt;), frontIsWangTile(bool).\n\nJSON encoding used by these Forms:\nVector3 is a string: "x|y|z".\nList&lt;T&gt; is [{"v":value}].\nDictionary&lt;K,V&gt; is [{"k":key,"v":value}].\nEnums use integer values. The existing id/uid is always preserved by SetStory and cannot be changed.\nParameter objects use: uid, name, valueType, min, v, max; Character/Item/Skill parameters also have showType.\nEffect-clip objects use: uid(int), tex(int), time(float), pos(Vector3), rot(float), scale(Vector3), opacity(float), transition(bool).\nEvent-trigger objects use: uid, name, evt(list&lt;int&gt;), type(enum int).\nMap-model objects use: id, subPrefabUnitName(list&lt;int&gt;), subPrefabUnitPos(list&lt;Vector3&gt;), subPrefabUnitScale(list&lt;Vector3&gt;), subUnitTexsName(list&lt;list&lt;int&gt;&gt;), animTimeInterval(float), isObstacle(bool), colliderScale(float).\n\nExamples:\nAddStoryCharacter "New Hero"\nSetStoryCharacter "New Hero" {"size":2,"enableNav":true,"passType":[{"v":1}]}\nSetStoryItem "Potion" {"price":10,"isConsume":true}\nSetStoryEffect "Spark" {"ground":true}\nSetStoryMission "Find Exit" {"targetPos":"3|0|5","radius":1.5}\n\nNames containing spaces must be enclosed in double quotes. JSON must be an object. These commands can only run from ModStory.</t>
+          <t xml:space="preserve">Story commands (command names are case-insensitive)\n\nFor every supported data type:\nAddStory&lt;Type&gt; "name" - create data from that type's default row.\nDelStory&lt;Type&gt; "name" - delete the named data.\nCopyStory&lt;Type&gt; "name" - copy it; duplicate names receive Copy, Copy 2, and so on.\nSetStory&lt;Type&gt; "name" {JSON} - update only the supplied JSON fields.\n\nAll Story commands:\nCharacter: AddStoryCharacter, DelStoryCharacter, CopyStoryCharacter, SetStoryCharacter\nItem: AddStoryItem, DelStoryItem, CopyStoryItem, SetStoryItem\nSkill: AddStorySkill, DelStorySkill, CopyStorySkill, SetStorySkill\nSceneObject: AddStorySceneObject, DelStorySceneObject, CopyStorySceneObject, SetStorySceneObject\nEffect: AddStoryEffect, DelStoryEffect, CopyStoryEffect, SetStoryEffect\nEvent: AddStoryEvent, DelStoryEvent, CopyStoryEvent, SetStoryEvent\nMission: AddStoryMission, DelStoryMission, CopyStoryMission, SetStoryMission\nTile: AddStoryTile, DelStoryTile, CopyStoryTile, SetStoryTile\n\nSetStory JSON fields:\nCharacter: name(string), labId(int), avatarTex(int), paramDic(dictionary), protoUid(int), animDic(dictionary), defaultAnimName(dictionary), faceType(enum int), speedParamName(string), hpParamName(string), events(dictionary), equips(dictionary), desc(string), illustration(int), unique(bool), skill(dictionary), recoveryTime(float), enableNav(bool), minimapIcon(int), size(int), passType(list&lt;int&gt;).\nItem: name(string), labId(int), iconTexName(int), paramDic(dictionary), protoUid(int), model(object), desc(string), amount(int), maxAmountPer(int), equip(enum int), styleTex(dictionary), price(int), canEquipe(bool), events(dictionary), isConsume(bool), paramDicCharacter(dictionary), minimapIcon(int).\nSkill: name(string), labId(int), protoUid(int), icon(int), paramDic(dictionary), skillTypes(list&lt;enum int&gt;), characterUid(int), cd(float), lastUseTime(float), events(dictionary), triggerConditionUid(int).\nSceneObject: name(string), icon(int), model(object), labId(int), collision(bool), events(dictionary), paramDic(dictionary), minimapIcon(int), faceType(enum int), animClip(dictionary), isWangTile(bool), boundsCollision(bool), centerCollider(bool).\nEffect: name(string), labId(int), clips(list&lt;list&lt;EffectClip&gt;&gt;), ground(bool).\nEvent: name(string), code(string), zCode(list&lt;string&gt;), zCodeMap(list&lt;int&gt;), paramCount(int), returnValue(string), labId(int).\nMission: name(string), labId(int), desc(string), show(bool), received(bool), done(bool), fail(bool), targetSceneId(int), targetPos(Vector3), radius(float).\nTile: name(string), icon(int), animTimeInterval(float), texs(list&lt;int&gt;), labId(int), events(dictionary), isWangTile(bool), passType(int), enableFrontPart(bool), frontPartTexs(list&lt;int&gt;), frontIsWangTile(bool).\n\nJSON encoding used by these Forms:\nVector3 is a string: "x|y|z".\nList&lt;T&gt; is [{"v":value}].\nDictionary&lt;K,V&gt; is [{"k":key,"v":value}].\nEnums use integer values. The existing id/uid is always preserved by SetStory and cannot be changed.\nParameter objects use: uid, name, valueType, min, v, max; Character/Item/Skill parameters also have showType.\nEffect-clip objects use: uid(int), tex(int), time(float), pos(Vector3), rot(float), scale(Vector3), opacity(float), transition(bool).\nEvent-trigger objects use: uid, name, evt(list&lt;int&gt;), type(enum int).\nMap-model objects use: id, subPrefabUnitName(list&lt;int&gt;), subPrefabUnitPos(list&lt;Vector3&gt;), subPrefabUnitScale(list&lt;Vector3&gt;), subUnitTexsName(list&lt;list&lt;int&gt;&gt;), animTimeInterval(float), isObstacle(bool), colliderScale(float).\n\nExamples:\nAddStoryCharacter "New Hero"\nSetStoryCharacter "New Hero" {"size":2,"enableNav":true,"passType":[{"v":1}]}\nSetStoryItem "Potion" {"price":10,"isConsume":true}\nSetStoryEffect "Spark" {"ground":true}\nSetStoryMission "Find Exit" {"targetPos":"3|0|5","radius":1.5}\n\nNames containing spaces must be enclosed in double quotes. JSON must be an object. These commands can only run from ModStory.</t>
         </is>
       </c>
       <c r="D357" s="0" t="inlineStr">
         <is>
-          <t>Story 指令（指令名不区分大小写）\n\n每种受支持的数据类型都有以下操作：\nAddStory&lt;类型&gt; "名称" - 根据该类型的默认数据新增。\nDelStory&lt;类型&gt; "名称" - 删除指定名称的数据。\nCopyStory&lt;类型&gt; "名称" - 复制数据；重名时自动使用 Copy、Copy 2 等后缀。\nSetStory&lt;类型&gt; "名称" {JSON} - 只更新 JSON 中提供的字段。\n\n全部 Story 指令：\n人物 Character：AddStoryCharacter、DelStoryCharacter、CopyStoryCharacter、SetStoryCharacter\n道具 Item：AddStoryItem、DelStoryItem、CopyStoryItem、SetStoryItem\n技能 Skill：AddStorySkill、DelStorySkill、CopyStorySkill、SetStorySkill\n场景物体 SceneObject：AddStorySceneObject、DelStorySceneObject、CopyStorySceneObject、SetStorySceneObject\n特效 Effect：AddStoryEffect、DelStoryEffect、CopyStoryEffect、SetStoryEffect\n事件 Event：AddStoryEvent、DelStoryEvent、CopyStoryEvent、SetStoryEvent\n任务 Mission：AddStoryMission、DelStoryMission、CopyStoryMission、SetStoryMission\n地面贴图 Tile：AddStoryTile、DelStoryTile、CopyStoryTile、SetStoryTile\n\nSetStory 可用 JSON 字段：\nCharacter：name(文本)、labId(整数)、avatarTex(整数)、paramDic(字典)、protoUid(整数)、animDic(字典)、defaultAnimName(字典)、faceType(枚举整数)、speedParamName(文本)、hpParamName(文本)、events(字典)、equips(字典)、desc(文本)、illustration(整数)、unique(布尔)、skill(字典)、recoveryTime(小数)、enableNav(布尔)、minimapIcon(整数)、size(整数)、passType(整数列表)。\nItem：name(文本)、labId(整数)、iconTexName(整数)、paramDic(字典)、protoUid(整数)、model(对象)、desc(文本)、amount(整数)、maxAmountPer(整数)、equip(枚举整数)、styleTex(字典)、price(整数)、canEquipe(布尔)、events(字典)、isConsume(布尔)、paramDicCharacter(字典)、minimapIcon(整数)。\nSkill：name(文本)、labId(整数)、protoUid(整数)、icon(整数)、paramDic(字典)、skillTypes(枚举整数列表)、characterUid(整数)、cd(小数)、lastUseTime(小数)、events(字典)、triggerConditionUid(整数)。\nSceneObject：name(文本)、icon(整数)、model(对象)、labId(整数)、collision(布尔)、events(字典)、paramDic(字典)、minimapIcon(整数)、faceType(枚举整数)、animClip(字典)。\nEffect：name(文本)、labId(整数)、clips(特效帧二维列表)、ground(布尔)。\nEvent：name(文本)、code(文本)、zCode(文本列表)、zCodeMap(整数列表)、paramCount(整数)、returnValue(文本)、labId(整数)。\nMission：name(文本)、labId(整数)、desc(文本)、show(布尔)、received(布尔)、done(布尔)、fail(布尔)、targetSceneId(整数)、targetPos(Vector3)、radius(小数)。\nTile：name(文本)、icon(整数)、animTimeInterval(小数)、texs(整数列表)、labId(整数)、events(字典)、isWangTile(布尔)、passType(整数)、enableFrontPart(布尔)、frontPartTexs(整数列表)、frontIsWangTile(布尔)。\n\n这些 Form 使用的 JSON 编码：\nVector3 使用文本："x|y|z"。\nList&lt;T&gt; 使用 [{"v":值}]。\nDictionary&lt;K,V&gt; 使用 [{"k":键,"v":值}]。\n枚举使用整数。SetStory 始终保留原有 id/uid，不能通过 JSON 修改。\n参数对象字段：uid、name、valueType、min、v、max；人物/道具/技能参数还包含 showType。\n特效帧对象字段：uid(整数)、tex(整数)、time(小数)、pos(Vector3)、rot(小数)、scale(Vector3)、opacity(小数)、transition(布尔)。\n事件触发对象字段：uid、name、evt(整数列表)、type(枚举整数)。\n地图模型对象字段：id、subPrefabUnitName(整数列表)、subPrefabUnitPos(Vector3列表)、subPrefabUnitScale(Vector3列表)、subUnitTexsName(整数列表的列表)、animTimeInterval(小数)、isObstacle(布尔)、colliderScale(小数)。\n\n示例：\nAddStoryCharacter "新人物"\nSetStoryCharacter "新人物" {"size":2,"enableNav":true,"passType":[{"v":1}]}\nSetStoryItem "血瓶" {"price":10,"isConsume":true}\nSetStoryEffect "火花" {"ground":true}\nSetStoryMission "寻找出口" {"targetPos":"3|0|5","radius":1.5}\n\n名称包含空格时必须使用双引号。JSON 必须是对象。Story 指令只能在 ModStory 中执行。</t>
+          <t xml:space="preserve">Story 指令（指令名不区分大小写）\n\n每种受支持的数据类型都有以下操作：\nAddStory&lt;类型&gt; "名称" - 根据该类型的默认数据新增。\nDelStory&lt;类型&gt; "名称" - 删除指定名称的数据。\nCopyStory&lt;类型&gt; "名称" - 复制数据；重名时自动使用 Copy、Copy 2 等后缀。\nSetStory&lt;类型&gt; "名称" {JSON} - 只更新 JSON 中提供的字段。\n\n全部 Story 指令：\n人物 Character：AddStoryCharacter、DelStoryCharacter、CopyStoryCharacter、SetStoryCharacter\n道具 Item：AddStoryItem、DelStoryItem、CopyStoryItem、SetStoryItem\n技能 Skill：AddStorySkill、DelStorySkill、CopyStorySkill、SetStorySkill\n场景物体 SceneObject：AddStorySceneObject、DelStorySceneObject、CopyStorySceneObject、SetStorySceneObject\n特效 Effect：AddStoryEffect、DelStoryEffect、CopyStoryEffect、SetStoryEffect\n事件 Event：AddStoryEvent、DelStoryEvent、CopyStoryEvent、SetStoryEvent\n任务 Mission：AddStoryMission、DelStoryMission、CopyStoryMission、SetStoryMission\n地面贴图 Tile：AddStoryTile、DelStoryTile、CopyStoryTile、SetStoryTile\n\nSetStory 可用 JSON 字段：\nCharacter：name(文本)、labId(整数)、avatarTex(整数)、paramDic(字典)、protoUid(整数)、animDic(字典)、defaultAnimName(字典)、faceType(枚举整数)、speedParamName(文本)、hpParamName(文本)、events(字典)、equips(字典)、desc(文本)、illustration(整数)、unique(布尔)、skill(字典)、recoveryTime(小数)、enableNav(布尔)、minimapIcon(整数)、size(整数)、passType(整数列表)。\nItem：name(文本)、labId(整数)、iconTexName(整数)、paramDic(字典)、protoUid(整数)、model(对象)、desc(文本)、amount(整数)、maxAmountPer(整数)、equip(枚举整数)、styleTex(字典)、price(整数)、canEquipe(布尔)、events(字典)、isConsume(布尔)、paramDicCharacter(字典)、minimapIcon(整数)。\nSkill：name(文本)、labId(整数)、protoUid(整数)、icon(整数)、paramDic(字典)、skillTypes(枚举整数列表)、characterUid(整数)、cd(小数)、lastUseTime(小数)、events(字典)、triggerConditionUid(整数)。\nSceneObject：name(文本)、icon(整数)、model(对象)、labId(整数)、collision(布尔)、events(字典)、paramDic(字典)、minimapIcon(整数)、faceType(枚举整数)、animClip(字典)、isWangTile(布尔)、boundsCollision(布尔)、centerCollider(布尔)。\nEffect：name(文本)、labId(整数)、clips(特效帧二维列表)、ground(布尔)。\nEvent：name(文本)、code(文本)、zCode(文本列表)、zCodeMap(整数列表)、paramCount(整数)、returnValue(文本)、labId(整数)。\nMission：name(文本)、labId(整数)、desc(文本)、show(布尔)、received(布尔)、done(布尔)、fail(布尔)、targetSceneId(整数)、targetPos(Vector3)、radius(小数)。\nTile：name(文本)、icon(整数)、animTimeInterval(小数)、texs(整数列表)、labId(整数)、events(字典)、isWangTile(布尔)、passType(整数)、enableFrontPart(布尔)、frontPartTexs(整数列表)、frontIsWangTile(布尔)。\n\n这些 Form 使用的 JSON 编码：\nVector3 使用文本："x|y|z"。\nList&lt;T&gt; 使用 [{"v":值}]。\nDictionary&lt;K,V&gt; 使用 [{"k":键,"v":值}]。\n枚举使用整数。SetStory 始终保留原有 id/uid，不能通过 JSON 修改。\n参数对象字段：uid、name、valueType、min、v、max；人物/道具/技能参数还包含 showType。\n特效帧对象字段：uid(整数)、tex(整数)、time(小数)、pos(Vector3)、rot(小数)、scale(Vector3)、opacity(小数)、transition(布尔)。\n事件触发对象字段：uid、name、evt(整数列表)、type(枚举整数)。\n地图模型对象字段：id、subPrefabUnitName(整数列表)、subPrefabUnitPos(Vector3列表)、subPrefabUnitScale(Vector3列表)、subUnitTexsName(整数列表的列表)、animTimeInterval(小数)、isObstacle(布尔)、colliderScale(小数)。\n\n示例：\nAddStoryCharacter "新人物"\nSetStoryCharacter "新人物" {"size":2,"enableNav":true,"passType":[{"v":1}]}\nSetStoryItem "血瓶" {"price":10,"isConsume":true}\nSetStoryEffect "火花" {"ground":true}\nSetStoryMission "寻找出口" {"targetPos":"3|0|5","radius":1.5}\n\n名称包含空格时必须使用双引号。JSON 必须是对象。Story 指令只能在 ModStory 中执行。</t>
         </is>
       </c>
     </row>
@@ -8133,6 +8133,40 @@
       <c r="D361" s="0" t="inlineStr">
         <is>
           <t>没有可用的操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n" s="0">
+        <v>1000368</v>
+      </c>
+      <c r="B362" t="str" s="0">
+        <v>boundsCollision</v>
+      </c>
+      <c r="C362" t="str" s="0">
+        <v>Texture bounds collision</v>
+      </c>
+      <c r="D362" t="str" s="0">
+        <v>贴图边界碰撞</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="0">
+        <v>1000369</v>
+      </c>
+      <c r="B363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">centerCollider</t>
+        </is>
+      </c>
+      <c r="C363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Center collider</t>
+        </is>
+      </c>
+      <c r="D363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碰撞体居中</t>
         </is>
       </c>
     </row>
